--- a/Excel/促销赠品获取参数化.xlsx
+++ b/Excel/促销赠品获取参数化.xlsx
@@ -28,7 +28,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>场景</t>
   </si>
@@ -52,6 +55,21 @@
   </si>
   <si>
     <t>单笔订单满125点21212（赠品）</t>
+  </si>
+  <si>
+    <t>获取200促销</t>
+  </si>
+  <si>
+    <t>获取126促销</t>
+  </si>
+  <si>
+    <t>单笔订单满126点（赠品）</t>
+  </si>
+  <si>
+    <t>获取127促销</t>
+  </si>
+  <si>
+    <t>单笔订单满127点（赠品）</t>
   </si>
   <si>
     <t>pcno</t>
@@ -1247,84 +1265,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="27.8761061946903" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5575221238938" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5575221238938" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.5575221238938" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.02654867256637" style="1"/>
+    <col min="1" max="1" width="9.02654867256637" style="1"/>
+    <col min="2" max="2" width="27.8761061946903" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5575221238938" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5575221238938" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.5575221238938" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.02654867256637" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="27" spans="1:5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" ht="27" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
         <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1352,30 +1420,30 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="40.5" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1">
         <v>60003152</v>
@@ -1387,18 +1455,18 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1">
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1">
         <v>60003154</v>
@@ -1410,18 +1478,18 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1">
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="40.5" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1">
         <v>60003156</v>
@@ -1433,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1"/>

--- a/Excel/促销赠品获取参数化.xlsx
+++ b/Excel/促销赠品获取参数化.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
   <si>
     <t>序号</t>
   </si>
@@ -51,7 +51,7 @@
     <t>["30112012","30122012"]</t>
   </si>
   <si>
-    <t>单笔订单满125点（赠品）</t>
+    <t>单笔订单满200点（赠品）</t>
   </si>
   <si>
     <t>单笔订单满125点21212（赠品）</t>
@@ -63,13 +63,7 @@
     <t>获取126促销</t>
   </si>
   <si>
-    <t>单笔订单满126点（赠品）</t>
-  </si>
-  <si>
     <t>获取127促销</t>
-  </si>
-  <si>
-    <t>单笔订单满127点（赠品）</t>
   </si>
   <si>
     <t>pcno</t>
@@ -1375,7 +1369,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1383,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1392,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1423,10 +1417,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1435,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1443,7 +1437,7 @@
     </row>
     <row r="2" ht="40.5" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1">
         <v>60003152</v>
@@ -1455,18 +1449,18 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1">
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1">
         <v>60003154</v>
@@ -1478,18 +1472,18 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1">
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="40.5" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1">
         <v>60003156</v>
@@ -1501,13 +1495,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1"/>
